--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:09</t>
+    <t xml:space="preserve">2026-09-09 23:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:03</t>
+    <t xml:space="preserve">2026-09-17 14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:00</t>
+    <t xml:space="preserve">2026-09-23 12:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -657,7 +657,9 @@
       <c r="C11" s="2" t="n">
         <v>11302</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E11" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:29</t>
+    <t xml:space="preserve">2026-10-02 14:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:15</t>
+    <t xml:space="preserve">2026-10-04 08:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:51</t>
+    <t xml:space="preserve">2026-10-05 10:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -525,7 +525,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>942689.12</v>
+        <v>942689.13</v>
       </c>
     </row>
     <row r="4">
